--- a/Vanco/data/Vanco Stats.xlsx
+++ b/Vanco/data/Vanco Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/golpira/Python/University of Calgary/UofC-Git/Ben Wajda/Vanco/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00878CCF-CC75-5E49-B5E4-AE5C0F79B4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA0F17-76C0-264E-A0ED-80CD2ED42794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="1420" windowWidth="25660" windowHeight="17940" activeTab="4" xr2:uid="{2F12B353-2824-944D-A3AA-6A430BC1237A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="48">
   <si>
     <t>Study ID</t>
   </si>
@@ -181,13 +181,19 @@
   </si>
   <si>
     <t>Fixed-Golpira</t>
+  </si>
+  <si>
+    <t>This was correct</t>
+  </si>
+  <si>
+    <t>Fixed by Golpira</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -214,6 +220,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="8" tint="0.59999389629810485"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -270,21 +283,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -666,25 +683,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>85</v>
+      </c>
+      <c r="H2" s="7">
+        <v>3</v>
+      </c>
+      <c r="I2" s="7">
         <v>80</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>85</v>
+      <c r="J2" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -720,23 +740,23 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
+        <v>4</v>
+      </c>
+      <c r="G6" s="8">
+        <v>570</v>
+      </c>
+      <c r="H6" s="8">
         <v>14</v>
       </c>
-      <c r="G6" s="6">
+      <c r="I6" s="8">
         <v>747</v>
       </c>
-      <c r="H6" s="6">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6">
-        <v>570</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="J6" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -822,7 +842,7 @@
       <c r="F11">
         <v>8</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>1181</v>
       </c>
     </row>
@@ -965,13 +985,13 @@
       <c r="B2" s="1">
         <v>43</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>2887</v>
       </c>
       <c r="D2" s="1">
         <v>55</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>1297</v>
       </c>
       <c r="F2" s="1"/>
@@ -1013,9 +1033,654 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>64</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>515</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>232</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1181</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2">
+        <v>572</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>488</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2">
+        <v>564</v>
+      </c>
+      <c r="D12" s="2">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1359</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>502</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ED5EA8-9426-934A-A7D7-03DDFED4C388}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>13</v>
+      </c>
+      <c r="F6" s="7">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7">
+        <v>570</v>
+      </c>
+      <c r="H6" s="7">
+        <v>13</v>
+      </c>
+      <c r="I6" s="7">
+        <v>747</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>64</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>515</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>564</v>
+      </c>
+      <c r="D13" s="2">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1359</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <v>36</v>
+      </c>
+      <c r="G14" s="1">
+        <v>314</v>
+      </c>
+      <c r="H14" s="2">
+        <v>32</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2">
+        <v>418</v>
+      </c>
+      <c r="H16" s="2">
+        <v>6</v>
+      </c>
+      <c r="I16" s="2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2">
+        <v>4</v>
+      </c>
+      <c r="G17" s="2">
+        <v>502</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{084840DD-9D1E-4747-8749-A849D9031603}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>49</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1026,405 +1691,82 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="7">
+        <v>22</v>
+      </c>
+      <c r="G6" s="7">
+        <v>570</v>
+      </c>
+      <c r="H6" s="7">
+        <v>48</v>
+      </c>
+      <c r="I6" s="7">
+        <v>747</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1">
+        <v>7</v>
+      </c>
+      <c r="G7" s="1">
         <v>85</v>
       </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>100</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>100</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>64</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>515</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>232</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>1181</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="2">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2">
-        <v>572</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" s="2">
-        <v>488</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2">
-        <v>564</v>
-      </c>
-      <c r="D12" s="2">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1359</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>502</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>474</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ED5EA8-9426-934A-A7D7-03DDFED4C388}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2">
-        <v>570</v>
-      </c>
-      <c r="H6" s="2">
-        <v>13</v>
-      </c>
-      <c r="I6" s="2">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2">
-        <v>13</v>
-      </c>
-      <c r="I7" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>100</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <v>2</v>
       </c>
       <c r="G9" s="1">
         <v>64</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="2">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,19 +1775,19 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
         <v>515</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2">
         <v>507</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1458,31 +1800,39 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="B12" s="2">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2">
+        <v>572</v>
+      </c>
+      <c r="D12" s="2">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2">
+        <v>488</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2">
         <v>564</v>
       </c>
       <c r="D13" s="2">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2">
         <v>1359</v>
@@ -1492,342 +1842,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2">
-        <v>36</v>
-      </c>
-      <c r="G14" s="1">
-        <v>314</v>
-      </c>
-      <c r="H14" s="2">
-        <v>32</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2">
-        <v>418</v>
-      </c>
-      <c r="H16" s="2">
-        <v>6</v>
-      </c>
-      <c r="I16" s="2">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2">
-        <v>502</v>
-      </c>
-      <c r="H17" s="2">
-        <v>3</v>
-      </c>
-      <c r="I17" s="2">
-        <v>474</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{084840DD-9D1E-4747-8749-A849D9031603}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>49</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
-        <v>26</v>
-      </c>
-      <c r="G6" s="2">
-        <v>570</v>
-      </c>
-      <c r="H6" s="2">
-        <v>48</v>
-      </c>
-      <c r="I6" s="2">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1">
-        <v>7</v>
-      </c>
-      <c r="G7" s="1">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <v>6</v>
-      </c>
-      <c r="G9" s="1">
-        <v>64</v>
-      </c>
-      <c r="H9" s="2">
-        <v>4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>515</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2">
-        <v>29</v>
-      </c>
-      <c r="C12" s="2">
-        <v>572</v>
-      </c>
-      <c r="D12" s="2">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2">
-        <v>488</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2">
-        <v>564</v>
-      </c>
-      <c r="D13" s="2">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1359</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -1848,7 +1863,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1869,7 +1884,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1918,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BA5536-9D33-C74C-BB88-9E138ED00CA6}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -1932,7 +1947,7 @@
     <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,30 +1976,33 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>85</v>
+      </c>
+      <c r="H2" s="7">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
         <v>80</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1995,12 +2013,12 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -2017,17 +2035,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2045,17 +2063,17 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2068,11 +2086,11 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>1181</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2089,7 +2107,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -2106,17 +2124,17 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -2148,171 +2166,171 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2.34</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1.17</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>19.600000000000001</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>2.6</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>15.3</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>14.49</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>7.8</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>5.36</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>3.56</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>49</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>1.8</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>3.2</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>19</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
         <v>19</v>
       </c>
     </row>
